--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2327,35 +2327,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134759202</v>
+        <v>135432046</v>
       </c>
       <c r="B16" t="n">
-        <v>57386</v>
+        <v>57776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2367,13 +2372,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467209</v>
+        <v>467196</v>
       </c>
       <c r="R16" t="n">
-        <v>6550488</v>
+        <v>6550502</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2397,27 +2402,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>20:47</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>02:19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Noterad 3 ggr under perioden.</t>
+          <t>Noterad 1645 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,27 +2439,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134759036</v>
+        <v>134759202</v>
       </c>
       <c r="B17" t="n">
-        <v>57796</v>
+        <v>57386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102976</v>
+        <v>102954</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2473,11 +2468,6 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2489,13 +2479,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467121</v>
+        <v>467209</v>
       </c>
       <c r="R17" t="n">
-        <v>6550565</v>
+        <v>6550488</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,27 +2509,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>02:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Noterad 18 ggr under perioden.</t>
+          <t>Noterad 3 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,7 +2556,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134759442</v>
+        <v>134759036</v>
       </c>
       <c r="B18" t="n">
         <v>57796</v>
@@ -2611,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467209</v>
+        <v>467121</v>
       </c>
       <c r="R18" t="n">
-        <v>6550488</v>
+        <v>6550565</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2641,27 +2631,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Noterad 16 ggr under perioden.</t>
+          <t>Noterad 18 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,7 +2678,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134760475</v>
+        <v>134759442</v>
       </c>
       <c r="B19" t="n">
         <v>57796</v>
@@ -2719,7 +2709,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2733,10 +2723,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467132</v>
+        <v>467209</v>
       </c>
       <c r="R19" t="n">
-        <v>6550557</v>
+        <v>6550488</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2763,27 +2753,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>6 inspelningar under perioden</t>
+          <t>Noterad 16 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2810,7 +2800,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134760847</v>
+        <v>134760475</v>
       </c>
       <c r="B20" t="n">
         <v>57796</v>
@@ -2851,14 +2841,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Klingen, Stora Klingen, Nrk</t>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467235</v>
+        <v>467132</v>
       </c>
       <c r="R20" t="n">
-        <v>6550451</v>
+        <v>6550557</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2885,12 +2875,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,12 +2890,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4 noteringar under perioden</t>
+          <t>6 inspelningar under perioden</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,35 +2922,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134758923</v>
+        <v>134760847</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2968,17 +2963,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+          <t>Stora Klingen, Stora Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467121</v>
+        <v>467235</v>
       </c>
       <c r="R21" t="n">
-        <v>6550565</v>
+        <v>6550451</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3002,27 +2997,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Noterad 5 ggr under perioden.</t>
+          <t>4 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3049,7 +3044,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134759686</v>
+        <v>134758923</v>
       </c>
       <c r="B22" t="n">
         <v>58136</v>
@@ -3089,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467209</v>
+        <v>467121</v>
       </c>
       <c r="R22" t="n">
-        <v>6550488</v>
+        <v>6550565</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3119,22 +3114,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3166,7 +3161,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134760241</v>
+        <v>134759686</v>
       </c>
       <c r="B23" t="n">
         <v>58136</v>
@@ -3195,11 +3190,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3211,10 +3201,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467105</v>
+        <v>467209</v>
       </c>
       <c r="R23" t="n">
-        <v>6550506</v>
+        <v>6550488</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3241,27 +3231,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Noterad 5 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,7 +3278,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134760431</v>
+        <v>134760241</v>
       </c>
       <c r="B24" t="n">
         <v>58136</v>
@@ -3317,6 +3307,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3328,10 +3323,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467132</v>
+        <v>467105</v>
       </c>
       <c r="R24" t="n">
-        <v>6550557</v>
+        <v>6550506</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3358,27 +3353,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5 noteringar under perioden</t>
+          <t>Noterad 50 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3405,7 +3400,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134760766</v>
+        <v>134760431</v>
       </c>
       <c r="B25" t="n">
         <v>58136</v>
@@ -3441,14 +3436,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Klingen, Stora Klingen, Nrk</t>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467235</v>
+        <v>467132</v>
       </c>
       <c r="R25" t="n">
-        <v>6550451</v>
+        <v>6550557</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3475,12 +3470,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,12 +3485,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>6 noteringar under perioden</t>
+          <t>5 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,7 +3517,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134761030</v>
+        <v>134760766</v>
       </c>
       <c r="B26" t="n">
         <v>58136</v>
@@ -3558,14 +3553,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+          <t>Stora Klingen, Stora Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467108</v>
+        <v>467235</v>
       </c>
       <c r="R26" t="n">
-        <v>6550501</v>
+        <v>6550451</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3592,27 +3587,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>13 noteringar under perioden</t>
+          <t>6 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3639,32 +3634,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134757317</v>
+        <v>134761030</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3679,10 +3674,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467121</v>
+        <v>467108</v>
       </c>
       <c r="R27" t="n">
-        <v>6550565</v>
+        <v>6550501</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3709,27 +3704,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>13 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3756,38 +3751,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134759408</v>
+        <v>135431344</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3801,10 +3796,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467209</v>
+        <v>467110</v>
       </c>
       <c r="R28" t="n">
-        <v>6550488</v>
+        <v>6550492</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3831,27 +3826,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Noterad 178 ggr under perioden.</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3878,40 +3858,35 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134760264</v>
+        <v>135431910</v>
       </c>
       <c r="B29" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3923,10 +3898,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467105</v>
+        <v>467196</v>
       </c>
       <c r="R29" t="n">
-        <v>6550506</v>
+        <v>6550502</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3953,27 +3928,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>Noterad 3 ggr under 3 dagar under ovanstående periond.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4000,7 +3965,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134760456</v>
+        <v>134757317</v>
       </c>
       <c r="B30" t="n">
         <v>58131</v>
@@ -4040,10 +4005,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467132</v>
+        <v>467121</v>
       </c>
       <c r="R30" t="n">
-        <v>6550557</v>
+        <v>6550565</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4070,27 +4035,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 47 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4117,10 +4082,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134759572</v>
+        <v>134759408</v>
       </c>
       <c r="B31" t="n">
-        <v>58837</v>
+        <v>58131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4128,34 +4093,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208250</v>
+        <v>103023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467215</v>
+        <v>467209</v>
       </c>
       <c r="R31" t="n">
-        <v>6550470</v>
+        <v>6550488</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4182,27 +4157,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I liten göl vid rotvälta i våtmark</t>
+          <t>Noterad 178 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4229,10 +4204,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134759216</v>
+        <v>134760264</v>
       </c>
       <c r="B32" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4240,34 +4215,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467241</v>
+        <v>467105</v>
       </c>
       <c r="R32" t="n">
-        <v>6550560</v>
+        <v>6550506</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4294,22 +4279,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Noterad 82 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4336,10 +4326,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134759251</v>
+        <v>134760456</v>
       </c>
       <c r="B33" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,34 +4337,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467193</v>
+        <v>467132</v>
       </c>
       <c r="R33" t="n">
-        <v>6550523</v>
+        <v>6550557</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4401,22 +4396,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>138 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4440,6 +4440,556 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135431454</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Noterad 72 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135432229</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467196</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550502</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Noterad 50 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134759572</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467215</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550470</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I liten göl vid rotvälta i våtmark</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134759216</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>467241</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6550560</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134759251</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>467193</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6550523</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3965,35 +3965,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134757317</v>
+        <v>135442095</v>
       </c>
       <c r="B30" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4005,10 +4010,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467121</v>
+        <v>467102</v>
       </c>
       <c r="R30" t="n">
-        <v>6550565</v>
+        <v>6550498</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4035,27 +4040,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>Noterad 43 ggr under 4 dagar under perioden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4082,7 +4077,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134759408</v>
+        <v>134757317</v>
       </c>
       <c r="B31" t="n">
         <v>58131</v>
@@ -4111,11 +4106,6 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4127,10 +4117,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467209</v>
+        <v>467121</v>
       </c>
       <c r="R31" t="n">
-        <v>6550488</v>
+        <v>6550565</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4167,17 +4157,17 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Noterad 178 ggr under perioden.</t>
+          <t>Noterad 47 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4204,7 +4194,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134760264</v>
+        <v>134759408</v>
       </c>
       <c r="B32" t="n">
         <v>58131</v>
@@ -4249,10 +4239,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467105</v>
+        <v>467209</v>
       </c>
       <c r="R32" t="n">
-        <v>6550506</v>
+        <v>6550488</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4284,22 +4274,22 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>Noterad 178 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,7 +4316,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134760456</v>
+        <v>134760264</v>
       </c>
       <c r="B33" t="n">
         <v>58131</v>
@@ -4355,6 +4345,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4366,10 +4361,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467132</v>
+        <v>467105</v>
       </c>
       <c r="R33" t="n">
-        <v>6550557</v>
+        <v>6550506</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4396,27 +4391,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 82 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4443,7 +4438,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135431454</v>
+        <v>134760456</v>
       </c>
       <c r="B34" t="n">
         <v>58131</v>
@@ -4472,11 +4467,6 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4488,10 +4478,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467110</v>
+        <v>467132</v>
       </c>
       <c r="R34" t="n">
-        <v>6550492</v>
+        <v>6550557</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4518,17 +4508,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Noterad 72 ggr under perioden.</t>
+          <t>138 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135432229</v>
+        <v>135431454</v>
       </c>
       <c r="B35" t="n">
         <v>58131</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467196</v>
+        <v>467110</v>
       </c>
       <c r="R35" t="n">
-        <v>6550502</v>
+        <v>6550492</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4630,17 +4630,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Noterad 72 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134759572</v>
+        <v>135432229</v>
       </c>
       <c r="B36" t="n">
-        <v>58837</v>
+        <v>58131</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4678,34 +4678,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208250</v>
+        <v>103023</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467215</v>
+        <v>467196</v>
       </c>
       <c r="R36" t="n">
-        <v>6550470</v>
+        <v>6550502</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4732,27 +4742,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I liten göl vid rotvälta i våtmark</t>
+          <t>Noterad 50 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134759216</v>
+        <v>135442068</v>
       </c>
       <c r="B37" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4790,34 +4790,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467241</v>
+        <v>467102</v>
       </c>
       <c r="R37" t="n">
-        <v>6550560</v>
+        <v>6550498</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4844,22 +4854,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Noterad 212 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4886,10 +4891,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134759251</v>
+        <v>134759572</v>
       </c>
       <c r="B38" t="n">
-        <v>106324</v>
+        <v>58837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4897,21 +4902,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>208250</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4921,10 +4926,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467193</v>
+        <v>467215</v>
       </c>
       <c r="R38" t="n">
-        <v>6550523</v>
+        <v>6550470</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4951,22 +4956,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>I liten göl vid rotvälta i våtmark</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4990,6 +5000,220 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134759216</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>467241</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6550560</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134759251</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>467193</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6550523</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4891,10 +4891,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134759572</v>
+        <v>135484433</v>
       </c>
       <c r="B38" t="n">
-        <v>58837</v>
+        <v>56842</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4902,34 +4902,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208250</v>
+        <v>205992</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467215</v>
+        <v>467207</v>
       </c>
       <c r="R38" t="n">
-        <v>6550470</v>
+        <v>6550465</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4956,27 +4966,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>I liten göl vid rotvälta i våtmark</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5003,10 +5008,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134759216</v>
+        <v>135484477</v>
       </c>
       <c r="B39" t="n">
-        <v>106324</v>
+        <v>56854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,34 +5019,44 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>205995</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467241</v>
+        <v>467207</v>
       </c>
       <c r="R39" t="n">
-        <v>6550560</v>
+        <v>6550465</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5068,22 +5083,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>03:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>03:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5110,10 +5125,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134759251</v>
+        <v>135484901</v>
       </c>
       <c r="B40" t="n">
-        <v>106324</v>
+        <v>56854</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5121,34 +5136,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>205995</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467193</v>
+        <v>467134</v>
       </c>
       <c r="R40" t="n">
-        <v>6550523</v>
+        <v>6550499</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5175,22 +5200,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5214,6 +5239,675 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135484452</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>467207</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6550465</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135485124</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135484812</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56856</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134759572</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>467215</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6550470</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I liten göl vid rotvälta i våtmark</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134759216</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>467241</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6550560</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134759251</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>467193</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6550523</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759073</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759346</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759289</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760159</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760749</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759147</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,6 +2018,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759789</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2085,6 +2145,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756998</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2202,6 +2267,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759570</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2324,6 +2394,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760738</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2436,6 +2511,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432046</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,6 +2633,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759202</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2675,6 +2760,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759036</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2797,6 +2887,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759442</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2919,6 +3014,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760475</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3041,6 +3141,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760847</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3158,6 +3263,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134758923</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3275,6 +3385,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759686</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3397,6 +3512,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760241</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3514,6 +3634,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760431</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3631,6 +3756,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760766</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3748,6 +3878,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761030</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3855,6 +3990,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431344</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3962,6 +4102,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431910</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4074,6 +4219,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442095</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4191,6 +4341,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134757317</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4313,6 +4468,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759408</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4435,6 +4595,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760264</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4552,6 +4717,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760456</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4664,6 +4834,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431454</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4776,6 +4951,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432229</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4888,6 +5068,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442068</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5005,6 +5190,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484433</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5122,6 +5312,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484477</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5239,6 +5434,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484901</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5352,6 +5552,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484452</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5465,6 +5670,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485124</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5582,6 +5792,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484812</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5694,6 +5909,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759572</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5801,6 +6021,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759216</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5908,8 +6133,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -2405,7 +2405,7 @@
         <v>135432046</v>
       </c>
       <c r="B16" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>135431344</v>
       </c>
       <c r="B28" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>135431910</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>135442095</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>135431454</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>135432229</v>
       </c>
       <c r="B36" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>135442068</v>
       </c>
       <c r="B37" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>135484433</v>
       </c>
       <c r="B38" t="n">
-        <v>56842</v>
+        <v>56847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>135484477</v>
       </c>
       <c r="B39" t="n">
-        <v>56854</v>
+        <v>56859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>135484901</v>
       </c>
       <c r="B40" t="n">
-        <v>56854</v>
+        <v>56859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135484452</v>
       </c>
       <c r="B41" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>135485124</v>
       </c>
       <c r="B42" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>135484812</v>
       </c>
       <c r="B43" t="n">
-        <v>56856</v>
+        <v>56861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 22870-2026 artfynd.xlsx
+++ b/artfynd/A 22870-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,35 +2402,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134759202</v>
+        <v>135432046</v>
       </c>
       <c r="B16" t="n">
-        <v>57386</v>
+        <v>57781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>102118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2442,13 +2447,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467209</v>
+        <v>467196</v>
       </c>
       <c r="R16" t="n">
-        <v>6550488</v>
+        <v>6550502</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,27 +2477,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>20:47</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>02:19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Noterad 3 ggr under perioden.</t>
+          <t>Noterad 1645 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2518,33 +2513,33 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759202</t>
+          <t>https://artportalen.se/Sighting/135432046</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134759036</v>
+        <v>134759202</v>
       </c>
       <c r="B17" t="n">
-        <v>57796</v>
+        <v>57386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102976</v>
+        <v>102954</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2553,11 +2548,6 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -2569,13 +2559,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467121</v>
+        <v>467209</v>
       </c>
       <c r="R17" t="n">
-        <v>6550565</v>
+        <v>6550488</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2599,27 +2589,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>02:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Noterad 18 ggr under perioden.</t>
+          <t>Noterad 3 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,13 +2635,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759036</t>
+          <t>https://artportalen.se/Sighting/134759202</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134759442</v>
+        <v>134759036</v>
       </c>
       <c r="B18" t="n">
         <v>57796</v>
@@ -2696,10 +2686,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467209</v>
+        <v>467121</v>
       </c>
       <c r="R18" t="n">
-        <v>6550488</v>
+        <v>6550565</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2726,27 +2716,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Noterad 16 ggr under perioden.</t>
+          <t>Noterad 18 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2772,13 +2762,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759442</t>
+          <t>https://artportalen.se/Sighting/134759036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134760475</v>
+        <v>134759442</v>
       </c>
       <c r="B19" t="n">
         <v>57796</v>
@@ -2809,7 +2799,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2823,10 +2813,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467132</v>
+        <v>467209</v>
       </c>
       <c r="R19" t="n">
-        <v>6550557</v>
+        <v>6550488</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2853,27 +2843,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>6 inspelningar under perioden</t>
+          <t>Noterad 16 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2899,13 +2889,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760475</t>
+          <t>https://artportalen.se/Sighting/134759442</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134760847</v>
+        <v>134760475</v>
       </c>
       <c r="B20" t="n">
         <v>57796</v>
@@ -2946,14 +2936,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stora Klingen, Stora Klingen, Nrk</t>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467235</v>
+        <v>467132</v>
       </c>
       <c r="R20" t="n">
-        <v>6550451</v>
+        <v>6550557</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2980,12 +2970,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2995,12 +2985,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4 noteringar under perioden</t>
+          <t>6 inspelningar under perioden</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3026,41 +3016,46 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760847</t>
+          <t>https://artportalen.se/Sighting/134760475</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134758923</v>
+        <v>134760847</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>57796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>102976</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3068,17 +3063,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+          <t>Stora Klingen, Stora Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467121</v>
+        <v>467235</v>
       </c>
       <c r="R21" t="n">
-        <v>6550565</v>
+        <v>6550451</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3102,27 +3097,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Noterad 5 ggr under perioden.</t>
+          <t>4 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,13 +3143,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134758923</t>
+          <t>https://artportalen.se/Sighting/134760847</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134759686</v>
+        <v>134758923</v>
       </c>
       <c r="B22" t="n">
         <v>58136</v>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467209</v>
+        <v>467121</v>
       </c>
       <c r="R22" t="n">
-        <v>6550488</v>
+        <v>6550565</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3224,22 +3219,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3270,13 +3265,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759686</t>
+          <t>https://artportalen.se/Sighting/134758923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134760241</v>
+        <v>134759686</v>
       </c>
       <c r="B23" t="n">
         <v>58136</v>
@@ -3305,11 +3300,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3321,10 +3311,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467105</v>
+        <v>467209</v>
       </c>
       <c r="R23" t="n">
-        <v>6550506</v>
+        <v>6550488</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3351,27 +3341,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Noterad 50 ggr under perioden.</t>
+          <t>Noterad 5 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3397,13 +3387,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760241</t>
+          <t>https://artportalen.se/Sighting/134759686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134760431</v>
+        <v>134760241</v>
       </c>
       <c r="B24" t="n">
         <v>58136</v>
@@ -3432,6 +3422,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -3443,10 +3438,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467132</v>
+        <v>467105</v>
       </c>
       <c r="R24" t="n">
-        <v>6550557</v>
+        <v>6550506</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3473,27 +3468,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5 noteringar under perioden</t>
+          <t>Noterad 50 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,13 +3514,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760431</t>
+          <t>https://artportalen.se/Sighting/134760241</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134760766</v>
+        <v>134760431</v>
       </c>
       <c r="B25" t="n">
         <v>58136</v>
@@ -3561,14 +3556,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stora Klingen, Stora Klingen, Nrk</t>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467235</v>
+        <v>467132</v>
       </c>
       <c r="R25" t="n">
-        <v>6550451</v>
+        <v>6550557</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3595,12 +3590,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3610,12 +3605,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>6 noteringar under perioden</t>
+          <t>5 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,13 +3636,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760766</t>
+          <t>https://artportalen.se/Sighting/134760431</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134761030</v>
+        <v>134760766</v>
       </c>
       <c r="B26" t="n">
         <v>58136</v>
@@ -3683,14 +3678,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+          <t>Stora Klingen, Stora Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467108</v>
+        <v>467235</v>
       </c>
       <c r="R26" t="n">
-        <v>6550501</v>
+        <v>6550451</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3717,27 +3712,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>13 noteringar under perioden</t>
+          <t>6 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3763,38 +3758,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134761030</t>
+          <t>https://artportalen.se/Sighting/134760766</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134757317</v>
+        <v>134761030</v>
       </c>
       <c r="B27" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467121</v>
+        <v>467108</v>
       </c>
       <c r="R27" t="n">
-        <v>6550565</v>
+        <v>6550501</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3839,27 +3834,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Noterad 47 ggr under perioden.</t>
+          <t>13 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3885,44 +3880,44 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134757317</t>
+          <t>https://artportalen.se/Sighting/134761030</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134759408</v>
+        <v>135431344</v>
       </c>
       <c r="B28" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3936,10 +3931,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467209</v>
+        <v>467110</v>
       </c>
       <c r="R28" t="n">
-        <v>6550488</v>
+        <v>6550492</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3966,27 +3961,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Noterad 178 ggr under perioden.</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,46 +3992,41 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759408</t>
+          <t>https://artportalen.se/Sighting/135431344</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134760264</v>
+        <v>135431910</v>
       </c>
       <c r="B29" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4063,10 +4038,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467105</v>
+        <v>467196</v>
       </c>
       <c r="R29" t="n">
-        <v>6550506</v>
+        <v>6550502</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4093,27 +4068,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:44</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Noterad 82 ggr under perioden.</t>
+          <t>Noterad 3 ggr under 3 dagar under ovanstående periond.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4139,41 +4104,46 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760264</t>
+          <t>https://artportalen.se/Sighting/135431910</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134760456</v>
+        <v>135442095</v>
       </c>
       <c r="B30" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4185,10 +4155,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467132</v>
+        <v>467102</v>
       </c>
       <c r="R30" t="n">
-        <v>6550557</v>
+        <v>6550498</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4215,27 +4185,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>06:10</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>138 noteringar under perioden</t>
+          <t>Noterad 43 ggr under 4 dagar under perioden.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4261,16 +4221,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134760456</t>
+          <t>https://artportalen.se/Sighting/135442095</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134759572</v>
+        <v>134757317</v>
       </c>
       <c r="B31" t="n">
-        <v>58837</v>
+        <v>58131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4278,34 +4238,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208250</v>
+        <v>103023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467215</v>
+        <v>467121</v>
       </c>
       <c r="R31" t="n">
-        <v>6550470</v>
+        <v>6550565</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4332,27 +4297,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I liten göl vid rotvälta i våtmark</t>
+          <t>Noterad 47 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4378,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759572</t>
+          <t>https://artportalen.se/Sighting/134757317</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134759216</v>
+        <v>134759408</v>
       </c>
       <c r="B32" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4395,34 +4360,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467241</v>
+        <v>467209</v>
       </c>
       <c r="R32" t="n">
-        <v>6550560</v>
+        <v>6550488</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4449,22 +4424,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Noterad 178 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4490,16 +4470,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759216</t>
+          <t>https://artportalen.se/Sighting/134759408</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134759251</v>
+        <v>134760264</v>
       </c>
       <c r="B33" t="n">
-        <v>106324</v>
+        <v>58131</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4507,34 +4487,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>103023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lilla Klingen, Lilla Klingen, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467193</v>
+        <v>467105</v>
       </c>
       <c r="R33" t="n">
-        <v>6550523</v>
+        <v>6550506</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4561,22 +4551,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Noterad 82 ggr under perioden.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4601,6 +4596,1544 @@
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760264</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134760456</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550557</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>138 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134760456</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135431454</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467110</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550492</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Noterad 72 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135431454</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135432229</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467196</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550502</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Noterad 50 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135432229</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135442068</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>467102</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6550498</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Noterad 212 ggr under perioden.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442068</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135484433</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56847</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>467207</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6550465</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484433</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135484477</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56859</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>467207</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6550465</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484477</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135484901</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56859</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484901</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135484452</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>467207</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6550465</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484452</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135485124</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135485124</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135484812</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56861</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>467134</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6550499</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484812</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134759572</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>467215</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6550470</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>I liten göl vid rotvälta i våtmark</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759572</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134759216</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>467241</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6550560</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759216</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134759251</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lilla Klingen, Lilla Klingen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>467193</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6550523</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134759251</t>
         </is>
@@ -4640,6 +6173,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
